--- a/data/trans_orig/P15B_3_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007 (tasa de respuesta: 51,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -1076,97 +1076,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5055</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5568</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23163</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49193</t>
+          <t>49078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71974</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>154790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>180116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>35678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52529</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>61925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>54766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61364</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73550</t>
+          <t>73811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86261</t>
+          <t>87090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,62 +5120,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>43245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>60228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45689</t>
+          <t>45302</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>48312</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>57470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100756</t>
+          <t>101539</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36352</t>
+          <t>36523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94567</t>
+          <t>94118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>210324</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>238230</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>232272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>447810</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>482133</t>
+          <t>482927</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>28710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28802</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59742</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71007</t>
+          <t>71172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -9094,82 +9094,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>3963</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>54881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62894</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>169496</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>331998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>357507</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>45397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53926</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56126</t>
+          <t>56180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34206</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19496</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>22019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,62 +12109,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41105</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>74193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86183</t>
+          <t>86552</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36912</t>
+          <t>36320</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48787</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>78884</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>138300</t>
+          <t>137991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188532</t>
+          <t>189042</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>203576</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>331412</t>
+          <t>333849</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>362891</t>
+          <t>365119</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15B_3_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Provincia-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15925</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>58,33%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>89342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>154790</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>180116</t>
+          <t>179267</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>52615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>61368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>46244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>73599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87090</t>
+          <t>86216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43245</t>
+          <t>42309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27564</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>48166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60228</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>36349</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>43910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45302</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48312</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57470</t>
+          <t>57463</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80869</t>
+          <t>80493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101539</t>
+          <t>100448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59450</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94118</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>210342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>238230</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248400</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>448259</t>
+          <t>449529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>482927</t>
+          <t>481928</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>27610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>35517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71172</t>
+          <t>71118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>62856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>43092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51771</t>
+          <t>51790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60393</t>
+          <t>60405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177318</t>
+          <t>177725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>183533</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>330532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>357533</t>
+          <t>356432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26069</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>50854</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22360</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52052</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44543</t>
+          <t>46212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56180</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,22 +11418,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,27 +11531,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>44143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>732</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,27 +11874,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>42246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,27 +12560,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>50386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>41270</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>52742</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>101478</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74193</t>
+          <t>93244</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86552</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>20374</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>25552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27931</t>
+          <t>33068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47614</t>
+          <t>52043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>84630</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>152643</t>
+          <t>170405</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>137991</t>
+          <t>153568</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>182665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>215610</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>189042</t>
+          <t>205906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>203576</t>
+          <t>221520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>350474</t>
+          <t>386015</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>367461</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>365119</t>
+          <t>400048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
